--- a/templates/SH_Project_Report_Extended_v1.xlsx
+++ b/templates/SH_Project_Report_Extended_v1.xlsx
@@ -1055,7 +1055,7 @@
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" hidden="1">
+    <row r="1" spans="1:10" hidden="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="25.5" customHeight="1">
+    <row r="2" spans="1:10" ht="25.5" customHeight="1">
       <c r="A2" s="36" t="s">
         <v>7</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>SUMMARY_HDR</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>

--- a/templates/SH_Project_Report_Extended_v1.xlsx
+++ b/templates/SH_Project_Report_Extended_v1.xlsx
@@ -36,28 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -799,70 +777,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/templates/SH_Project_Report_Extended_v1.xlsx
+++ b/templates/SH_Project_Report_Extended_v1.xlsx
@@ -36,6 +36,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -777,6 +799,70 @@
 </styleSheet>
 </file>
 
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -959,7 +1045,7 @@
   <sheetPr>
     <tabColor rgb="FF1A1A2E"/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="28" customWidth="1"/>
@@ -969,7 +1055,7 @@
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" hidden="1">
+    <row r="1" spans="1:7" hidden="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1015,22 +1101,22 @@
         <v>13</v>
       </c>
       <c r="H2" s="36" t="s">
-        <v>LINKEDIN_HDR</v>
+        <v>87</v>
       </c>
       <c r="I2" s="36" t="s">
-        <v>BIO_HDR</v>
+        <v>88</v>
       </c>
       <c r="J2" s="36" t="s">
-        <v>SUMMARY_HDR</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:J2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
